--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Id</t>
   </si>
@@ -55,7 +55,43 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>string</t>
+    <t>string[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通知客户端类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoticeClientType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中目标时间点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中自身时间点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitActionTimes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitActionTimes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -184,7 +220,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -219,7 +255,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -428,18 +464,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:F9"/>
+  <dimension ref="C3:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.6640625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="12.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -452,8 +489,17 @@
       <c r="F3" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -466,8 +512,17 @@
       <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -480,11 +535,20 @@
       <c r="F5" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -92,6 +92,26 @@
   </si>
   <si>
     <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中行为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中自身行为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitAction</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -464,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:I9"/>
+  <dimension ref="C3:K9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -472,11 +492,15 @@
     <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="7" max="7" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -493,13 +517,19 @@
         <v>10</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -516,13 +546,19 @@
         <v>11</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -539,16 +575,22 @@
         <v>12</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:9" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
   <si>
     <t>Id</t>
   </si>
@@ -112,6 +112,22 @@
   </si>
   <si>
     <t>SelfHitAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Buffs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中自身Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfBuffs</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -484,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:K9"/>
+  <dimension ref="C3:M9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -496,11 +512,11 @@
     <col min="8" max="8" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="11" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -528,8 +544,14 @@
       <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="L3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -557,8 +579,14 @@
       <c r="K4" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="L4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -586,11 +614,17 @@
       <c r="K5" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="L5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:11" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -128,6 +128,22 @@
   </si>
   <si>
     <t>SelfBuffs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能开始时的自身特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中时的目标特效</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -500,7 +516,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:M9"/>
+  <dimension ref="C3:O9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -513,10 +529,12 @@
     <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="14" max="14" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -550,8 +568,14 @@
       <c r="M3" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="N3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -585,8 +609,14 @@
       <c r="M4" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="N4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -620,11 +650,17 @@
       <c r="M5" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="N5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="6" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:13" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
   <si>
     <t>Id</t>
   </si>
@@ -144,6 +144,22 @@
   </si>
   <si>
     <t>技能命中时的目标特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>起手动画</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartAnimation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中动画</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitAnimation</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -516,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:O9"/>
+  <dimension ref="C3:Q9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -530,11 +546,11 @@
     <col min="10" max="10" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="15" max="17" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -574,8 +590,14 @@
       <c r="O3" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="P3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="4" spans="3:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -615,8 +637,14 @@
       <c r="O4" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="P4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="5" spans="3:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -656,11 +684,17 @@
       <c r="O5" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="P5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="6" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:15" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
   <si>
     <t>Id</t>
   </si>
@@ -147,19 +147,23 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>起手动画</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>StartAnimation</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>命中动画</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>HitAnimation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>"5"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>起手动画(motiontype)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中动画(motiontype)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -167,7 +171,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +197,14 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -221,13 +233,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -544,9 +557,12 @@
     <col min="8" max="8" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -591,10 +607,10 @@
         <v>31</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="3:17" x14ac:dyDescent="0.3">
@@ -638,10 +654,10 @@
         <v>30</v>
       </c>
       <c r="P4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="5" spans="3:17" x14ac:dyDescent="0.3">
@@ -691,13 +707,47 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1000</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2001</v>
+      </c>
+      <c r="O6" s="1">
+        <v>2</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>2</v>
+      </c>
+    </row>
     <row r="7" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -164,6 +164,30 @@
   </si>
   <si>
     <t>命中动画(motiontype)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷却时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoolDown</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StatusSkill</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>状态技能标志(只允许有一个状态技能在释放)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -545,28 +569,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:Q9"/>
+  <dimension ref="C3:S9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
-    <col min="3" max="4" width="12.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="33.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="16" max="16" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -574,46 +599,52 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -621,46 +652,52 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:19" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -668,31 +705,31 @@
         <v>8</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>16</v>
@@ -701,13 +738,19 @@
         <v>16</v>
       </c>
       <c r="P5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -715,36 +758,42 @@
         <v>1000</v>
       </c>
       <c r="E6" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F6" s="1">
         <v>1</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>1001</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>2001</v>
-      </c>
-      <c r="O6" s="1">
-        <v>2</v>
-      </c>
-      <c r="P6" s="1">
-        <v>1</v>
       </c>
       <c r="Q6" s="1">
         <v>2</v>
       </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:17" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>Id</t>
   </si>
@@ -188,6 +188,14 @@
   </si>
   <si>
     <t>状态技能标志(只允许有一个状态技能在释放)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束行为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FinishAction</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -569,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:S9"/>
+  <dimension ref="C3:T9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
@@ -585,13 +593,14 @@
     <col min="13" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="2"/>
+    <col min="16" max="16" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -632,19 +641,22 @@
         <v>26</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="T3" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -685,19 +697,22 @@
         <v>27</v>
       </c>
       <c r="P4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="3:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -744,13 +759,16 @@
         <v>16</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="T5" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="6" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -781,19 +799,22 @@
       <c r="O6" s="1">
         <v>2001</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="P6" s="1">
+        <v>1001</v>
+      </c>
+      <c r="R6" s="1">
         <v>2</v>
       </c>
-      <c r="R6" s="1">
+      <c r="S6" s="1">
         <v>1</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:19" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="64">
   <si>
     <t>Id</t>
   </si>
@@ -196,6 +196,131 @@
   </si>
   <si>
     <t>FinishAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能描述</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#火球术</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#虚空法球</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>#野蛮冲撞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球术释放</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火球术伤害结算</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空法球释放</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虚空法球结算</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲撞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>冲撞范围结算</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,0,1009,1011</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,0,1,800</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0018,30016,0,0</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名字</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ame</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -203,7 +328,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,6 +363,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -265,7 +397,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -273,6 +405,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -577,180 +712,197 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:T9"/>
+  <dimension ref="B2:V38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.77734375" style="2" customWidth="1"/>
-    <col min="3" max="5" width="12.6640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="33.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="12.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="12.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="33.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="12.21875" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="16" max="16" width="8.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="20.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="D2" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="V3" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="R4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:22" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>16</v>
@@ -762,59 +914,887 @@
         <v>16</v>
       </c>
       <c r="S5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="V5" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1">
         <v>1000</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>2000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="J6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>2</v>
       </c>
-      <c r="J6" s="1">
+      <c r="L6" s="1">
         <v>1001</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>0</v>
       </c>
-      <c r="O6" s="1">
+      <c r="Q6" s="1">
         <v>2001</v>
       </c>
-      <c r="P6" s="1">
+      <c r="R6" s="1">
         <v>1001</v>
-      </c>
-      <c r="R6" s="1">
-        <v>2</v>
-      </c>
-      <c r="S6" s="1">
-        <v>1</v>
       </c>
       <c r="T6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="3:20" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="U6" s="1">
+        <v>1</v>
+      </c>
+      <c r="V6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>2</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="O8" s="1">
+        <v>500</v>
+      </c>
+      <c r="U8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>3</v>
+      </c>
+      <c r="K9" s="1">
+        <v>2</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+    </row>
+    <row r="11" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1">
+        <v>2</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="M11" s="1">
+        <v>500</v>
+      </c>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1">
+        <v>1</v>
+      </c>
+      <c r="V11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1">
+        <v>3</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1">
+        <v>2</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>1008</v>
+      </c>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+    </row>
+    <row r="14" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1">
+        <v>2</v>
+      </c>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1">
+        <v>1</v>
+      </c>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1">
+        <v>1</v>
+      </c>
+      <c r="V14" s="1"/>
+    </row>
+    <row r="15" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="1">
+        <v>100</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1">
+        <v>3</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1">
+        <v>2</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1012</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+    </row>
+    <row r="17" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+    </row>
+    <row r="18" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+    </row>
+    <row r="19" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+    </row>
+    <row r="20" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+    </row>
+    <row r="21" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+    </row>
+    <row r="22" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+    </row>
+    <row r="23" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+    </row>
+    <row r="24" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+    </row>
+    <row r="25" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+    </row>
+    <row r="26" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+    </row>
+    <row r="27" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="1"/>
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+    </row>
+    <row r="36" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+    </row>
+    <row r="38" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -79,10 +79,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>HitActionTimes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>int[]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -321,6 +317,10 @@
       </rPr>
       <t>ame</t>
     </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitActionTimes</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -737,7 +737,7 @@
   <sheetData>
     <row r="2" spans="2:22" x14ac:dyDescent="0.3">
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.3">
@@ -745,19 +745,19 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>3</v>
@@ -769,37 +769,37 @@
         <v>10</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="V3" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.3">
@@ -807,19 +807,19 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>6</v>
@@ -831,37 +831,37 @@
         <v>11</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="S4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="T4" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="U4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="V4" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.3">
@@ -869,19 +869,19 @@
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>8</v>
@@ -893,31 +893,31 @@
         <v>12</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U5" s="3" t="s">
         <v>8</v>
@@ -931,10 +931,10 @@
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F6" s="1">
         <v>1000</v>
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6" s="1">
         <v>2</v>
@@ -978,7 +978,7 @@
     </row>
     <row r="7" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -986,10 +986,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F8" s="1">
         <v>1000</v>
@@ -1015,10 +1015,10 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1073,10 +1073,10 @@
         <v>4</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" s="1">
         <v>1000</v>
@@ -1118,10 +1118,10 @@
         <v>5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -1182,10 +1182,10 @@
         <v>6</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F14" s="1">
         <v>1000</v>
@@ -1206,14 +1206,14 @@
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
       <c r="N14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R14" s="1"/>
       <c r="S14" s="1">
@@ -1231,10 +1231,10 @@
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
